--- a/data/trans_orig/P36BPD12_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD12_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que consumen frutos secos a la semana en 2023</t>
+          <t>Población según el número de veces que consumen frutos secos a la semana en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79771</t>
+          <t>80453</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145194</t>
+          <t>140799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116809</t>
+          <t>117868</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>163919</t>
+          <t>164162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207321</t>
+          <t>206601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>288823</t>
+          <t>286258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152894</t>
+          <t>155604</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>219573</t>
+          <t>218972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102665</t>
+          <t>102062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147610</t>
+          <t>143751</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>272260</t>
+          <t>273279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>352328</t>
+          <t>355285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76291</t>
+          <t>74675</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139833</t>
+          <t>140628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31260</t>
+          <t>33602</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68623</t>
+          <t>70641</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>120763</t>
+          <t>117803</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>197634</t>
+          <t>193237</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97203</t>
+          <t>98470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147982</t>
+          <t>148253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93579</t>
+          <t>90406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>188430</t>
+          <t>184294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206531</t>
+          <t>209730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>312642</t>
+          <t>315794</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>177810</t>
+          <t>177854</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>230089</t>
+          <t>233485</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>121154</t>
+          <t>113043</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>236265</t>
+          <t>235727</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>306897</t>
+          <t>305198</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>448594</t>
+          <t>445904</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77547</t>
+          <t>76664</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119182</t>
+          <t>122789</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97843</t>
+          <t>101004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>295000</t>
+          <t>308506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194495</t>
+          <t>196385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>418116</t>
+          <t>429840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>46,04%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151909</t>
+          <t>152504</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>198054</t>
+          <t>197501</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>176156</t>
+          <t>175604</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211979</t>
+          <t>211640</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>336497</t>
+          <t>336878</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>395677</t>
+          <t>396406</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>215525</t>
+          <t>217031</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265080</t>
+          <t>264701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>220126</t>
+          <t>221167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258652</t>
+          <t>259211</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>451742</t>
+          <t>445254</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>513699</t>
+          <t>507547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,18%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100719</t>
+          <t>100853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142190</t>
+          <t>141942</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93046</t>
+          <t>93643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125333</t>
+          <t>123594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202121</t>
+          <t>203545</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251560</t>
+          <t>254789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91737</t>
+          <t>93162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>310013</t>
+          <t>308200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185961</t>
+          <t>187171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243366</t>
+          <t>245147</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>250703</t>
+          <t>279405</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>525003</t>
+          <t>531665</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>390774</t>
+          <t>391173</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>733372</t>
+          <t>730981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>253717</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>328288</t>
+          <t>327010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>686223</t>
+          <t>684377</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1158383</t>
+          <t>1115582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58816</t>
+          <t>62910</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>197556</t>
+          <t>198602</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>155825</t>
+          <t>156592</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>283273</t>
+          <t>279477</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>185789</t>
+          <t>199669</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>407992</t>
+          <t>416561</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170370</t>
+          <t>168550</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211311</t>
+          <t>209805</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186872</t>
+          <t>188250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>219136</t>
+          <t>223557</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>368380</t>
+          <t>367620</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>420381</t>
+          <t>422265</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>224823</t>
+          <t>224587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>267134</t>
+          <t>268907</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>217798</t>
+          <t>217898</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>253773</t>
+          <t>252279</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>454509</t>
+          <t>453905</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>509585</t>
+          <t>510555</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105400</t>
+          <t>105188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141653</t>
+          <t>142838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93154</t>
+          <t>93307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120824</t>
+          <t>121700</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207436</t>
+          <t>207138</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>253908</t>
+          <t>255432</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>117772</t>
+          <t>118312</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>148355</t>
+          <t>148038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63888</t>
+          <t>70055</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>231782</t>
+          <t>232059</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>156225</t>
+          <t>149746</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>364052</t>
+          <t>365353</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>146329</t>
+          <t>146226</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>176398</t>
+          <t>176289</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>261571</t>
+          <t>259801</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>514418</t>
+          <t>503182</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>422707</t>
+          <t>419430</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>738966</t>
+          <t>745633</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61476</t>
+          <t>61397</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>85214</t>
+          <t>85426</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30083</t>
+          <t>34701</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119209</t>
+          <t>122858</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>81531</t>
+          <t>79779</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>195701</t>
+          <t>195381</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>109973</t>
+          <t>111019</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>137044</t>
+          <t>137720</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>211525</t>
+          <t>214351</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>241365</t>
+          <t>241980</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>330635</t>
+          <t>332024</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>370433</t>
+          <t>370457</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>104954</t>
+          <t>104318</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>132777</t>
+          <t>129530</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>138257</t>
+          <t>138322</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>165780</t>
+          <t>165150</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>251012</t>
+          <t>250592</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>288655</t>
+          <t>288419</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31228</t>
+          <t>31181</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50414</t>
+          <t>50036</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36487</t>
+          <t>37134</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>55697</t>
+          <t>56082</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>72372</t>
+          <t>73715</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>98000</t>
+          <t>98723</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>842879</t>
+          <t>819866</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1170384</t>
+          <t>1169226</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1012179</t>
+          <t>1033252</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1388886</t>
+          <t>1388564</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2040403</t>
+          <t>2067202</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2524077</t>
+          <t>2531120</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1542506</t>
+          <t>1545399</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2070194</t>
+          <t>2122918</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1481323</t>
+          <t>1494700</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2010684</t>
+          <t>2023782</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3083933</t>
+          <t>3069504</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3845222</t>
+          <t>3828642</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>548334</t>
+          <t>510350</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>769799</t>
+          <t>766420</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>613826</t>
+          <t>616878</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>912251</t>
+          <t>920378</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1251466</t>
+          <t>1249143</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1617410</t>
+          <t>1631000</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD12_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD12_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>107539</t>
+          <t>115332</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80453</t>
+          <t>84457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>140799</t>
+          <t>146707</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>140395</t>
+          <t>158305</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117868</t>
+          <t>132984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164162</t>
+          <t>185717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>247934</t>
+          <t>273637</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206601</t>
+          <t>232666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>286258</t>
+          <t>313589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>188399</t>
+          <t>188956</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155604</t>
+          <t>156282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>218972</t>
+          <t>219961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>123481</t>
+          <t>142433</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102062</t>
+          <t>117320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143751</t>
+          <t>166838</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>311881</t>
+          <t>331390</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>273279</t>
+          <t>291245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>355285</t>
+          <t>372597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>104049</t>
+          <t>103505</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74675</t>
+          <t>74943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140628</t>
+          <t>135123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48032</t>
+          <t>60500</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33602</t>
+          <t>41369</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70641</t>
+          <t>82282</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152080</t>
+          <t>164005</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117803</t>
+          <t>131962</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>193237</t>
+          <t>202019</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>311908</t>
+          <t>361238</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>311908</t>
+          <t>361238</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>311908</t>
+          <t>361238</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>711895</t>
+          <t>769032</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>711895</t>
+          <t>769032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>711895</t>
+          <t>769032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>122125</t>
+          <t>137212</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98470</t>
+          <t>110569</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148253</t>
+          <t>162773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>153554</t>
+          <t>163936</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90406</t>
+          <t>143230</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184294</t>
+          <t>186112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>275679</t>
+          <t>301148</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209730</t>
+          <t>265667</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315794</t>
+          <t>333114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202849</t>
+          <t>228941</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>177854</t>
+          <t>201707</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>233485</t>
+          <t>259821</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>197605</t>
+          <t>231779</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>113043</t>
+          <t>210537</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>235727</t>
+          <t>255409</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>400454</t>
+          <t>460720</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>305198</t>
+          <t>425911</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445904</t>
+          <t>500525</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>97230</t>
+          <t>109403</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76664</t>
+          <t>87034</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122789</t>
+          <t>134160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>160345</t>
+          <t>105368</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101004</t>
+          <t>86376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>308506</t>
+          <t>125651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>257575</t>
+          <t>214771</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>196385</t>
+          <t>185081</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>429840</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>422204</t>
+          <t>475556</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>422204</t>
+          <t>475556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422204</t>
+          <t>475556</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>933708</t>
+          <t>976639</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933708</t>
+          <t>976639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933708</t>
+          <t>976639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>174918</t>
+          <t>196499</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>152504</t>
+          <t>171540</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>197501</t>
+          <t>222312</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>192970</t>
+          <t>213989</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>175604</t>
+          <t>194029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211640</t>
+          <t>234070</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>367889</t>
+          <t>410488</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>336878</t>
+          <t>377210</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>396406</t>
+          <t>441148</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>240606</t>
+          <t>279741</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217031</t>
+          <t>253077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>264701</t>
+          <t>306059</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,27 +1785,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>240075</t>
+          <t>277357</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>221167</t>
+          <t>256759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259211</t>
+          <t>297386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>480681</t>
+          <t>557098</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>445254</t>
+          <t>524598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>507547</t>
+          <t>590775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>119203</t>
+          <t>142915</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100853</t>
+          <t>121090</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141942</t>
+          <t>169866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>107917</t>
+          <t>129216</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93643</t>
+          <t>111755</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123594</t>
+          <t>146808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>227120</t>
+          <t>272131</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203545</t>
+          <t>243579</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>254789</t>
+          <t>301046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>534728</t>
+          <t>619155</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>534728</t>
+          <t>619155</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>534728</t>
+          <t>619155</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>540962</t>
+          <t>620562</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>540962</t>
+          <t>620562</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>540962</t>
+          <t>620562</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1075690</t>
+          <t>1239716</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1075690</t>
+          <t>1239716</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1075690</t>
+          <t>1239716</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>214553</t>
+          <t>223471</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93162</t>
+          <t>198051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>308200</t>
+          <t>251438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>221386</t>
+          <t>238767</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187171</t>
+          <t>219958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>245147</t>
+          <t>258808</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>435939</t>
+          <t>462238</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>279405</t>
+          <t>430894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>531665</t>
+          <t>495419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>536623</t>
+          <t>324211</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>391173</t>
+          <t>296808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>730981</t>
+          <t>351512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>302543</t>
+          <t>328479</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>253717</t>
+          <t>307606</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>327010</t>
+          <t>349351</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>839166</t>
+          <t>652690</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>684377</t>
+          <t>618224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1115582</t>
+          <t>685821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>135935</t>
+          <t>152208</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62910</t>
+          <t>130513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>198602</t>
+          <t>175303</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>188024</t>
+          <t>168690</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156592</t>
+          <t>150946</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>279477</t>
+          <t>186930</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>323959</t>
+          <t>320898</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>199669</t>
+          <t>294310</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>416561</t>
+          <t>351210</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>887112</t>
+          <t>699889</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>887112</t>
+          <t>699889</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>887112</t>
+          <t>699889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>711952</t>
+          <t>735936</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>711952</t>
+          <t>735936</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>711952</t>
+          <t>735936</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1599064</t>
+          <t>1435825</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1599064</t>
+          <t>1435825</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1599064</t>
+          <t>1435825</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,67 +2549,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>189902</t>
+          <t>198555</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168550</t>
+          <t>175858</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209805</t>
+          <t>220059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>36,18%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>227816</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>210530</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>248320</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>37,45%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>204428</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>188250</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>223557</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>37,34%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>394329</t>
+          <t>426370</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>367620</t>
+          <t>397136</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>422265</t>
+          <t>456254</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>247178</t>
+          <t>275512</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>224587</t>
+          <t>255114</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268907</t>
+          <t>302452</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>236001</t>
+          <t>260355</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>217898</t>
+          <t>239582</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>252279</t>
+          <t>279075</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>483179</t>
+          <t>535867</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>453905</t>
+          <t>505190</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>510555</t>
+          <t>566172</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>123124</t>
+          <t>134198</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105188</t>
+          <t>113974</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>142838</t>
+          <t>153885</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>106986</t>
+          <t>120187</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93307</t>
+          <t>106585</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>121700</t>
+          <t>136581</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>230111</t>
+          <t>254385</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207138</t>
+          <t>229620</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255432</t>
+          <t>280799</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>547415</t>
+          <t>608358</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547415</t>
+          <t>608358</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>547415</t>
+          <t>608358</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1107619</t>
+          <t>1216622</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1107619</t>
+          <t>1216622</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1107619</t>
+          <t>1216622</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>133740</t>
+          <t>144252</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118312</t>
+          <t>127185</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>148038</t>
+          <t>159596</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>149767</t>
+          <t>163963</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>70055</t>
+          <t>149273</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>232059</t>
+          <t>179407</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>283506</t>
+          <t>308215</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>149746</t>
+          <t>286657</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>365353</t>
+          <t>329655</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>161363</t>
+          <t>176395</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>146226</t>
+          <t>161075</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>176289</t>
+          <t>194172</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>382372</t>
+          <t>191249</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>259801</t>
+          <t>175582</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>503182</t>
+          <t>206315</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>543736</t>
+          <t>367644</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>419430</t>
+          <t>344125</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>745633</t>
+          <t>389597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>72460</t>
+          <t>85870</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61397</t>
+          <t>71527</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>85426</t>
+          <t>100047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>76229</t>
+          <t>83954</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>71493</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>122858</t>
+          <t>95104</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>148689</t>
+          <t>169824</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>79779</t>
+          <t>150326</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>195381</t>
+          <t>186691</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>367563</t>
+          <t>406517</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>367563</t>
+          <t>406517</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>367563</t>
+          <t>406517</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>975931</t>
+          <t>845683</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>975931</t>
+          <t>845683</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>975931</t>
+          <t>845683</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>123611</t>
+          <t>132600</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111019</t>
+          <t>117351</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>137720</t>
+          <t>148207</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>226931</t>
+          <t>244937</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>214351</t>
+          <t>229235</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>241980</t>
+          <t>260095</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>350542</t>
+          <t>377538</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>332024</t>
+          <t>355557</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>370457</t>
+          <t>398319</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>117876</t>
+          <t>129658</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>104318</t>
+          <t>116029</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>129530</t>
+          <t>144563</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>152562</t>
+          <t>167032</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>138322</t>
+          <t>152363</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>165150</t>
+          <t>182107</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>270438</t>
+          <t>296690</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>250592</t>
+          <t>275678</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>288419</t>
+          <t>318041</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,17%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>39778</t>
+          <t>46406</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31181</t>
+          <t>35378</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>57692</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>45570</t>
+          <t>51858</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37134</t>
+          <t>41641</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>56082</t>
+          <t>63252</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>85348</t>
+          <t>98265</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>73715</t>
+          <t>84171</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>98723</t>
+          <t>112676</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>281265</t>
+          <t>308665</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>281265</t>
+          <t>308665</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>281265</t>
+          <t>308665</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425063</t>
+          <t>463827</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425063</t>
+          <t>463827</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425063</t>
+          <t>463827</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>706327</t>
+          <t>772493</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>706327</t>
+          <t>772493</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>706327</t>
+          <t>772493</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1066388</t>
+          <t>1147921</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>819866</t>
+          <t>1086313</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1169226</t>
+          <t>1208431</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1289430</t>
+          <t>1411713</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1033252</t>
+          <t>1357625</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1388564</t>
+          <t>1462032</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2355818</t>
+          <t>2559634</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2067202</t>
+          <t>2479688</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2531120</t>
+          <t>2639314</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1694895</t>
+          <t>1603414</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1545399</t>
+          <t>1542257</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2122918</t>
+          <t>1668941</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1634639</t>
+          <t>1598684</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1494700</t>
+          <t>1548051</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2023782</t>
+          <t>1656664</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3329534</t>
+          <t>3202098</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3069504</t>
+          <t>3120985</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3828642</t>
+          <t>3278085</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>691780</t>
+          <t>774504</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>510350</t>
+          <t>714044</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>766420</t>
+          <t>827131</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>733102</t>
+          <t>719773</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>616878</t>
+          <t>677799</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>920378</t>
+          <t>763996</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1424881</t>
+          <t>1494277</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1249143</t>
+          <t>1424424</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1631000</t>
+          <t>1566402</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3453062</t>
+          <t>3525839</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3453062</t>
+          <t>3525839</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3453062</t>
+          <t>3525839</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3657172</t>
+          <t>3730170</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3657172</t>
+          <t>3730170</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3657172</t>
+          <t>3730170</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7110233</t>
+          <t>7256009</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7110233</t>
+          <t>7256009</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7110233</t>
+          <t>7256009</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
